--- a/stories/arbres/ATOM-REL.PAR.002-01.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.002-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Léa est au parc avec maman. Les oiseaux chantent. Léa aime la balançoire. Maya est déjà dessus. La balançoire va et vient. Léa a envie. Elle s'approche. Maman dit : on peut attendre. Attendre, c'est rester près. Léa pose les pieds au sol. Elle compte. Un. Deux. Trois. Maya se balance encore. Léa attend. Maman tient sa main. Le vent est doux. Maya descend. Maman dit : puis mon tour. Léa dit : puis mon tour. Léa s'assoit. Elle se balance. Ses cheveux bougent. Maya attend maintenant. Puis c'est encore le tour. Maman dit : on attend. Puis mon tour arrive. Léa sourit. Le bois de la balançoire est lisse. Une feuille tombe. Maman reste tout près.</t>
+          <t>Léa est au parc avec maman. Les oiseaux chantent. Léa aime la balançoire. Maya est déjà dessus. La balançoire va et vient. Léa a envie. Elle s'approche. On peut attendre. Attendre, c'est rester près. Léa pose les pieds au sol. Elle compte. Un. Deux. Trois. Maya se balance encore. Léa attend. Maman tient sa main. Le vent est doux. Maya descend. Puis mon tour. Puis mon tour. Léa s'assoit. Elle se balance. Ses cheveux bougent. Maya attend maintenant. Puis c'est encore le tour. On attend. Puis mon tour arrive. Léa sourit. Le bois de la balançoire est lisse. Une feuille tombe. Maman reste tout près.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,18 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Léa est au parc avec maman. Les oiseaux chantent. Léa aime la balançoire. Maya est déjà dessus. La balançoire va et vient. Léa a envie. Elle s'approche.
+maman|On peut attendre. Attendre, c'est rester près.
+narrateur|Léa pose les pieds au sol. Elle compte. Un. Deux. Trois. Maya se balance encore. Léa attend. Maman tient sa main. Le vent est doux. Maya descend.
+maman|Puis mon tour.
+enfant-f|Puis mon tour.
+narrateur|Léa s'assoit. Elle se balance. Ses cheveux bougent. Maya attend maintenant. Puis c'est encore le tour.
+maman|On attend.
+narrateur|Puis mon tour arrive. Léa sourit. Le bois de la balançoire est lisse. Une feuille tombe. Maman reste tout près.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1493,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Maya se balance. Que fait Léa ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1666,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a su attendre. Puis mon tour est venu. Elle s'est balancée. Maman est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1833,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Léa descend. Elle prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +2000,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2040,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.PAR.002-01.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.002-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1317,6 +1322,11 @@
 narrateur|Puis mon tour arrive. Léa sourit. Le bois de la balançoire est lisse. Une feuille tombe. Maman reste tout près.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1500,6 +1510,7 @@
           <t>narrateur|Maya se balance. Que fait Léa ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1671,6 +1682,7 @@
           <t>narrateur|Léa a su attendre. Puis mon tour est venu. Elle s'est balancée. Maman est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1838,6 +1850,7 @@
           <t>narrateur|Léa descend. Elle prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2005,6 +2018,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2023,7 +2037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2047,6 +2061,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2248,6 +2276,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.PAR.002-01.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.002-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Léa attend la balançoire</t>
+          <t>Mila attend la balançoire</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une plume tombe sur le sable. Mila veut la balançoire. Sarah s'y balance. Mila attend près de maman. Puis c'est son tour.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Léa est au parc avec maman. Les oiseaux chantent. Léa aime la balançoire. Maya est déjà dessus. La balançoire va et vient. Léa a envie. Elle s'approche. On peut attendre. Attendre, c'est rester près. Léa pose les pieds au sol. Elle compte. Un. Deux. Trois. Maya se balance encore. Léa attend. Maman tient sa main. Le vent est doux. Maya descend. Puis mon tour. Puis mon tour. Léa s'assoit. Elle se balance. Ses cheveux bougent. Maya attend maintenant. Puis c'est encore le tour. On attend. Puis mon tour arrive. Léa sourit. Le bois de la balançoire est lisse. Une feuille tombe. Maman reste tout près.</t>
+          <t>Une plume d'oiseau tombe tout doux. Elle se pose sur le sable. Le parc sent l'herbe. Un oiseau siffle deux notes. Maman pose le sac près du banc. Le banc sent le bois chaud. Une fourmi croise la plume. Tu as vu la plume, Mila ? Oui, maman. Elle est blanche. Elle est blanche, oui. La fourmi est petite. Toute petite. En ce moment, Mila a envie de se balancer. La chaîne de balançoire tinte. Sarah est déjà dessus. La balançoire va et vient. Moi aussi. On peut attendre. Attendre, c'est rester près. Mila pose les pieds au sol. Elle reste près de maman. Elle compte. Un. Deux. Trois. Tu attends. Bravo, Mila. Sarah se balance encore. Le vent est doux. Les cheveux de Sarah bougent. Maman tient la main de Mila. On attend. Puis mon tour. Puis mon tour. Mila souffle. Elle regarde la plume. La plume ne bouge pas. Encore un peu. On reste près. J'attends. Oui. C'est du bon travail. Sarah descend. Ses pieds touchent le sable. Puis mon tour. Puis mon tour. Mila s'assoit. Elle se balance. Ses cheveux bougent aussi. Le bois de la balançoire est lisse. Tu as su attendre. Puis ton tour est venu. C'est du bon travail. Tu vas haut ? Un peu. Le vent t'aide. Sarah attend maintenant. Elle reste près du banc. On attend. Puis c'est encore le tour. Une feuille tombe. Elle rejoint la plume. Tu aimes le vent ? Oui. Il pousse un peu. Il pousse, oui. Le sac est tiède au soleil.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1324,74 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Léa est au parc avec maman. Les oiseaux chantent. Léa aime la balançoire. Maya est déjà dessus. La balançoire va et vient. Léa a envie. Elle s'approche.
-maman|On peut attendre. Attendre, c'est rester près.
-narrateur|Léa pose les pieds au sol. Elle compte. Un. Deux. Trois. Maya se balance encore. Léa attend. Maman tient sa main. Le vent est doux. Maya descend.
+          <t>narrateur|Une plume d'oiseau tombe tout doux.
+narrateur|Elle se pose sur le sable.
+narrateur|Le parc sent l'herbe.
+narrateur|Un oiseau siffle deux notes.
+narrateur|Maman pose le sac près du banc.
+narrateur|Le banc sent le bois chaud.
+narrateur|Une fourmi croise la plume.
+maman|Tu as vu la plume, Mila ?
+enfant-f|Oui, maman.
+enfant-f|Elle est blanche.
+maman|Elle est blanche, oui.
+maman|La fourmi est petite.
+enfant-f|Toute petite.
+narrateur|En ce moment, Mila a envie de se balancer.
+narrateur|La chaîne de balançoire tinte.
+narrateur|Sarah est déjà dessus.
+narrateur|La balançoire va et vient.
+enfant-f|Moi aussi.
+maman|On peut attendre.
+maman|Attendre, c'est rester près.
+narrateur|Mila pose les pieds au sol.
+narrateur|Elle reste près de maman.
+narrateur|Elle compte.
+enfant-f|Un.
+enfant-f|Deux.
+enfant-f|Trois.
+maman|Tu attends.
+maman|Bravo, Mila.
+narrateur|Sarah se balance encore.
+narrateur|Le vent est doux.
+narrateur|Les cheveux de Sarah bougent.
+narrateur|Maman tient la main de Mila.
+maman|On attend.
 maman|Puis mon tour.
 enfant-f|Puis mon tour.
-narrateur|Léa s'assoit. Elle se balance. Ses cheveux bougent. Maya attend maintenant. Puis c'est encore le tour.
+narrateur|Mila souffle.
+narrateur|Elle regarde la plume.
+narrateur|La plume ne bouge pas.
+maman|Encore un peu.
+maman|On reste près.
+enfant-f|J'attends.
+maman|Oui.
+maman|C'est du bon travail.
+narrateur|Sarah descend.
+narrateur|Ses pieds touchent le sable.
+maman|Puis mon tour.
+enfant-f|Puis mon tour.
+narrateur|Mila s'assoit.
+narrateur|Elle se balance.
+narrateur|Ses cheveux bougent aussi.
+narrateur|Le bois de la balançoire est lisse.
+maman|Tu as su attendre.
+maman|Puis ton tour est venu.
+maman|C'est du bon travail.
+maman|Tu vas haut ?
+enfant-f|Un peu.
+maman|Le vent t'aide.
+narrateur|Sarah attend maintenant.
+narrateur|Elle reste près du banc.
 maman|On attend.
-narrateur|Puis mon tour arrive. Léa sourit. Le bois de la balançoire est lisse. Une feuille tombe. Maman reste tout près.</t>
+maman|Puis c'est encore le tour.
+narrateur|Une feuille tombe.
+narrateur|Elle rejoint la plume.
+maman|Tu aimes le vent ?
+enfant-f|Oui.
+enfant-f|Il pousse un peu.
+maman|Il pousse, oui.
+narrateur|Le sac est tiède au soleil.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1351,7 +1423,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Maya se balance. Que fait Léa ?</t>
+          <t>Sarah se balance. Que fait Mila ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1507,7 +1579,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Maya se balance. Que fait Léa ?</t>
+          <t>narrateur|Sarah se balance.
+narrateur|Que fait Mila ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1535,7 +1608,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Léa a su attendre. Puis mon tour est venu. Elle s'est balancée. Maman est là.</t>
+          <t>Mila a su attendre. Puis mon tour est venu. Elle s'est balancée. Tu as attendu. Puis ton tour. Bravo, Mila. C'est du bon travail. Tes pieds touchent le sable ? Un peu. On attend. Puis on joue. J'ai attendu près de toi. Oui. Près de moi. La plume est encore sur le sable. La chaîne tinte, plus loin.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1679,7 +1752,22 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Léa a su attendre. Puis mon tour est venu. Elle s'est balancée. Maman est là.</t>
+          <t>narrateur|Mila a su attendre.
+narrateur|Puis mon tour est venu.
+narrateur|Elle s'est balancée.
+maman|Tu as attendu.
+maman|Puis ton tour.
+maman|Bravo, Mila.
+maman|C'est du bon travail.
+maman|Tes pieds touchent le sable ?
+enfant-f|Un peu.
+maman|On attend.
+maman|Puis on joue.
+enfant-f|J'ai attendu près de toi.
+maman|Oui.
+maman|Près de moi.
+narrateur|La plume est encore sur le sable.
+narrateur|La chaîne tinte, plus loin.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1707,7 +1795,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Léa descend. Elle prend la main de maman.</t>
+          <t>Mila descend. Elle prend la main de maman. On va près du banc ? Oui. Ta main est tiède. J'ai attendu. Oui. Puis ton tour. Le sac attend près du banc. L'herbe sent encore. On range le sac ? Oui, maman. Maman ferme le sac. On reste un peu ? Oui. Le banc est chaud sous les jambes.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1847,7 +1935,22 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Léa descend. Elle prend la main de maman.</t>
+          <t>narrateur|Mila descend.
+narrateur|Elle prend la main de maman.
+maman|On va près du banc ?
+enfant-f|Oui.
+maman|Ta main est tiède.
+enfant-f|J'ai attendu.
+maman|Oui.
+maman|Puis ton tour.
+narrateur|Le sac attend près du banc.
+narrateur|L'herbe sent encore.
+maman|On range le sac ?
+enfant-f|Oui, maman.
+narrateur|Maman ferme le sac.
+maman|On reste un peu ?
+enfant-f|Oui.
+narrateur|Le banc est chaud sous les jambes.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1875,7 +1978,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai attendu. Puis mon tour. Bravo. Tu as fait du bon travail. La plume ne bouge plus. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2015,7 +2118,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai attendu.
+enfant-f|Puis mon tour.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|La plume ne bouge plus.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2037,7 +2145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2075,6 +2183,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.PAR.002-01.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.002-01.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une plume d'oiseau tombe tout doux. Elle se pose sur le sable. Le parc sent l'herbe. Un oiseau siffle deux notes. Maman pose le sac près du banc. Le banc sent le bois chaud. Une fourmi croise la plume. Tu as vu la plume, Mila ? Oui, maman. Elle est blanche. Elle est blanche, oui. La fourmi est petite. Toute petite. En ce moment, Mila a envie de se balancer. La chaîne de balançoire tinte. Sarah est déjà dessus. La balançoire va et vient. Moi aussi. On peut attendre. Attendre, c'est rester près. Mila pose les pieds au sol. Elle reste près de maman. Elle compte. Un. Deux. Trois. Tu attends. Bravo, Mila. Sarah se balance encore. Le vent est doux. Les cheveux de Sarah bougent. Maman tient la main de Mila. On attend. Puis mon tour. Puis mon tour. Mila souffle. Elle regarde la plume. La plume ne bouge pas. Encore un peu. On reste près. J'attends. Oui. C'est du bon travail. Sarah descend. Ses pieds touchent le sable. Puis mon tour. Puis mon tour. Mila s'assoit. Elle se balance. Ses cheveux bougent aussi. Le bois de la balançoire est lisse. Tu as su attendre. Puis ton tour est venu. C'est du bon travail. Tu vas haut ? Un peu. Le vent t'aide. Sarah attend maintenant. Elle reste près du banc. On attend. Puis c'est encore le tour. Une feuille tombe. Elle rejoint la plume. Tu aimes le vent ? Oui. Il pousse un peu. Il pousse, oui. Le sac est tiède au soleil.</t>
+          <t>Une plume d'oiseau tombe tout doux. Elle se pose sur le sable. Le parc sent l'herbe. Un oiseau siffle deux notes. Maman pose le sac près du banc. Le banc sent le bois chaud. Une fourmi croise la plume. Tu as vu la plume, Mila ? Oui, maman. Elle est blanche. Elle est blanche, oui. La fourmi est petite. Toute petite. En ce moment, Mila a envie de se balancer. La chaîne de balançoire tinte. Sarah est déjà dessus. La balançoire va et vient. Moi aussi. On peut attendre. Attendre, c'est rester près. Mila pose les pieds au sol. Elle reste près de maman. Elle compte. Un. Deux. Trois. Tu attends. Bravo, Mila. Sarah se balance encore. Le vent est doux. Les cheveux de Sarah bougent. Maman tient la main de Mila. On attend. Puis mon tour. Puis mon tour. Mila souffle. Elle regarde la plume. La plume ne bouge pas. Encore un peu. On reste près. J'attends. Oui. Sarah descend. Ses pieds touchent le sable. Puis mon tour. Puis mon tour. Mila s'assoit. Elle se balance. Ses cheveux bougent aussi. Le bois de la balançoire est lisse. Tu as su attendre. Puis ton tour est venu. Tu vas haut ? Un peu. Le vent t'aide. Sarah attend maintenant. Elle reste près du banc. On attend. Puis c'est encore le tour. Une feuille tombe. Elle rejoint la plume. Tu aimes le vent ? Oui. Il pousse un peu. Il pousse, oui. Le sac est tiède au soleil.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Léa est au parc avec maman. Les oiseaux chantent. Léa aime la balançoire. Maya est déjà dessus. La balançoire va et vient. Léa a envie. Elle s'approche. Maman dit : on peut &lt;emphasis level="moderate"&gt;attendre&lt;/emphasis&gt;. Attendre, c'est rester près. Léa pose les pieds au sol. Elle compte. Un. Deux. Trois. Maya se balance encore. Léa attend. Maman tient sa main. Le vent est doux. Maya descend. Maman dit : puis mon tour. Léa dit : puis mon tour. Léa s'assoit. Elle se balance. Ses cheveux bougent. Maya attend maintenant. Puis c'est encore le tour. Maman dit : on attend. Puis mon tour arrive. Léa sourit. Le bois de la balançoire est lisse. Une feuille tombe. Maman reste tout près.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une plume d'oiseau tombe tout doux. Elle se pose sur le sable. Le parc sent l'herbe. Un oiseau siffle deux notes. Maman pose le sac près du banc. Le banc sent le bois chaud. Une fourmi croise la plume. Tu as vu la plume, Mila ? Oui, maman. Elle est blanche. Elle est blanche, oui. La fourmi est petite. Toute petite. En ce moment, Mila a envie de se balancer. La chaîne de balançoire tinte. Sarah est déjà dessus. La balançoire va et vient. Moi aussi. On peut attendre. Attendre, c'est rester près. Mila pose les pieds au sol. Elle reste près de maman. Elle compte. Un. Deux. Trois. Tu attends. Bravo, Mila. Sarah se balance encore. Le vent est doux. Les cheveux de Sarah bougent. Maman tient la main de Mila. On attend. Puis mon tour. Puis mon tour. Mila souffle. Elle regarde la plume. La plume ne bouge pas. Encore un peu. On reste près. J'attends. Oui. Sarah descend. Ses pieds touchent le sable. Puis mon tour. Puis mon tour. Mila s'assoit. Elle se balance. Ses cheveux bougent aussi. Le bois de la balançoire est lisse. Tu as su attendre. Puis ton tour est venu. Tu vas haut ? Un peu. Le vent t'aide. Sarah attend maintenant. Elle reste près du banc. On attend. Puis c'est encore le tour. Une feuille tombe. Elle rejoint la plume. Tu aimes le vent ? Oui. Il pousse un peu. Il pousse, oui. Le sac est tiède au soleil.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1366,7 +1366,6 @@
 maman|On reste près.
 enfant-f|J'attends.
 maman|Oui.
-maman|C'est du bon travail.
 narrateur|Sarah descend.
 narrateur|Ses pieds touchent le sable.
 maman|Puis mon tour.
@@ -1377,7 +1376,6 @@
 narrateur|Le bois de la balançoire est lisse.
 maman|Tu as su attendre.
 maman|Puis ton tour est venu.
-maman|C'est du bon travail.
 maman|Tu vas haut ?
 enfant-f|Un peu.
 maman|Le vent t'aide.
@@ -1428,7 +1426,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Maya se balance. Que fait Léa ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah se balance. Que fait Mila ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1583,7 +1581,6 @@
 narrateur|Que fait Mila ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1608,12 +1605,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Mila a su attendre. Puis mon tour est venu. Elle s'est balancée. Tu as attendu. Puis ton tour. Bravo, Mila. C'est du bon travail. Tes pieds touchent le sable ? Un peu. On attend. Puis on joue. J'ai attendu près de toi. Oui. Près de moi. La plume est encore sur le sable. La chaîne tinte, plus loin.</t>
+          <t>Mila a su attendre. Puis mon tour est venu. Elle s'est balancée. Tu as attendu. Puis ton tour. Bravo, Mila. Tes pieds touchent le sable ? Un peu. On attend. Puis on joue. J'ai attendu près de toi. Oui. Près de moi. La plume est encore sur le sable. La chaîne tinte, plus loin.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Léa a su &lt;emphasis level="moderate"&gt;attendre&lt;/emphasis&gt;. Puis mon tour est venu. Elle s'est balancée. Maman est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila a su attendre. Puis mon tour est venu. Elle s'est balancée. Tu as attendu. Puis ton tour. Bravo, Mila. Tes pieds touchent le sable ? Un peu. On attend. Puis on joue. J'ai attendu près de toi. Oui. Près de moi. La plume est encore sur le sable. La chaîne tinte, plus loin.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1758,7 +1755,6 @@
 maman|Tu as attendu.
 maman|Puis ton tour.
 maman|Bravo, Mila.
-maman|C'est du bon travail.
 maman|Tes pieds touchent le sable ?
 enfant-f|Un peu.
 maman|On attend.
@@ -1770,7 +1766,6 @@
 narrateur|La chaîne tinte, plus loin.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1800,7 +1795,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Léa descend. Elle prend la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; de maman.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila descend. Elle prend la main de maman. On va près du banc ? Oui. Ta main est tiède. J'ai attendu. Oui. Puis ton tour. Le sac attend près du banc. L'herbe sent encore. On range le sac ? Oui, maman. Maman ferme le sac. On reste un peu ? Oui. Le banc est chaud sous les jambes.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1953,7 +1948,6 @@
 narrateur|Le banc est chaud sous les jambes.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1978,12 +1972,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai attendu. Puis mon tour. Bravo. Tu as fait du bon travail. La plume ne bouge plus. L'histoire est finie.</t>
+          <t>J'ai attendu. Puis mon tour. Bravo. La plume ne bouge plus.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai attendu. Puis mon tour. Bravo. La plume ne bouge plus.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2121,12 +2115,9 @@
           <t>enfant-f|J'ai attendu.
 enfant-f|Puis mon tour.
 maman|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|La plume ne bouge plus.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|La plume ne bouge plus.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2145,7 +2136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2190,6 +2181,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.PAR.002-01.xlsx
+++ b/stories/arbres/ATOM-REL.PAR.002-01.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Léa, Maya, maman</t>
+          <t>Mila, Sarah, maman</t>
         </is>
       </c>
     </row>
